--- a/results/Int All Data -0.8/Rando_2_permute.xlsx
+++ b/results/Int All Data -0.8/Rando_2_permute.xlsx
@@ -440,157 +440,157 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7429198288080094</v>
+        <v>0.7427093296842164</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.749465548659159</v>
+        <v>0.7422883314366304</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7482795274765938</v>
+        <v>0.7422883314366304</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7482795274765938</v>
+        <v>0.7463612974844831</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7574428720039657</v>
+        <v>0.7441997542431457</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7468196479812331</v>
+        <v>0.7428779384351153</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7482817965384588</v>
+        <v>0.737478618455502</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7525301785228058</v>
+        <v>0.7422441720018711</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.757162206505575</v>
+        <v>0.7425576516256955</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7569188932563481</v>
+        <v>0.742450133001934</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7578242489405227</v>
+        <v>0.7389690430144313</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7540274102673304</v>
+        <v>0.7421366533781095</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7536811165180722</v>
+        <v>0.7421366533781095</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7536811165180722</v>
+        <v>0.7447848231179004</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7554918278864212</v>
+        <v>0.7372262289588147</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7608866097423044</v>
+        <v>0.7200572850849327</v>
       </c>
     </row>
     <row r="18">
@@ -600,217 +600,217 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.752076366149786</v>
+        <v>0.7260462120630311</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7520084688370534</v>
+        <v>0.7141317172958368</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7458769400478946</v>
+        <v>0.7206140779579839</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7514143237148383</v>
+        <v>0.7263291466232868</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7529794527720954</v>
+        <v>0.730334215358407</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7548252473277433</v>
+        <v>0.7312746542298804</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7519360334005907</v>
+        <v>0.7426300870621583</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7576839161913274</v>
+        <v>0.747156865483031</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7582429781262436</v>
+        <v>0.7380071353268496</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7570241428182447</v>
+        <v>0.736718133644253</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7519733856497546</v>
+        <v>0.7367532168315518</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7593214806850472</v>
+        <v>0.7414904943762175</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7276272245533439</v>
+        <v>0.7412471811269907</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7231027151943364</v>
+        <v>0.7363367567076959</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7225787364467189</v>
+        <v>0.7360232770838715</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7225787364467189</v>
+        <v>0.7376608415775914</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7268972848056636</v>
+        <v>0.7336931250916352</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7306239571042581</v>
+        <v>0.724793515370276</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7281817483645301</v>
+        <v>0.7245502021210493</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7287034580502825</v>
+        <v>0.7246837276846493</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7423234146239293</v>
+        <v>0.7127341497301563</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7423234146239293</v>
+        <v>0.7120392931697748</v>
       </c>
     </row>
     <row r="40">
@@ -820,117 +820,117 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7426368942477537</v>
+        <v>0.7135625318541376</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7429503738715781</v>
+        <v>0.7197223366450001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7385265759507369</v>
+        <v>0.713452744168511</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7381780131396136</v>
+        <v>0.7237251363182551</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.737097241518945</v>
+        <v>0.7230981770706062</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7415889367525187</v>
+        <v>0.7223636991991957</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7439236268684851</v>
+        <v>0.7232339716960714</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7387348060126648</v>
+        <v>0.7213530939531246</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7387348060126648</v>
+        <v>0.7191610056482186</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.7520718280260559</v>
+        <v>0.720101444519692</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.755279059700763</v>
+        <v>0.7206933205800421</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7481765469765623</v>
+        <v>0.7145244395417193</v>
       </c>
     </row>
     <row r="52">
@@ -940,177 +940,177 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7486654425368811</v>
+        <v>0.7195027612737466</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7578570630659565</v>
+        <v>0.7193624285245512</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.7604305283074195</v>
+        <v>0.7218351823278479</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7619979264265417</v>
+        <v>0.7174464675943057</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7564491974502726</v>
+        <v>0.7218419895134434</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7533472153374619</v>
+        <v>0.7201693418324245</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.754189211832634</v>
+        <v>0.7274495395549846</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7524113145897187</v>
+        <v>0.7274495395549846</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7524113145897187</v>
+        <v>0.7276928528042114</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7524113145897187</v>
+        <v>0.7276928528042114</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7460013893640343</v>
+        <v>0.7379675140158206</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7460013893640343</v>
+        <v>0.7391489970746556</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.7489256864784858</v>
+        <v>0.7443797083033701</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7498310421626603</v>
+        <v>0.7443797083033701</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7489256864784858</v>
+        <v>0.7418390571873408</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7432762460640504</v>
+        <v>0.7364091921441587</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7448085609958739</v>
+        <v>0.7362711284568285</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.742925414191062</v>
+        <v>0.7276307154177517</v>
       </c>
     </row>
     <row r="70">
@@ -1120,867 +1120,867 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7367565331527393</v>
+        <v>0.7290577807876787</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7370677437146986</v>
+        <v>0.7254951791162527</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.7375917224623161</v>
+        <v>0.7309646654704638</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.7460692866767669</v>
+        <v>0.6669977169746772</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.7209727642758901</v>
+        <v>0.6607258554363231</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.7254689976331939</v>
+        <v>0.6727524069510092</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.7232395570791239</v>
+        <v>0.673206219324029</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.7220512668346937</v>
+        <v>0.7161642730973043</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.7225073482695785</v>
+        <v>0.709964846995413</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.6882305506489517</v>
+        <v>0.7091296576858361</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.6816123953613393</v>
+        <v>0.707733137379478</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.6965496296192863</v>
+        <v>0.715357359789431</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.6902404158317683</v>
+        <v>0.6893951030154086</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.692044320014522</v>
+        <v>0.6876172057724934</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.6969898276211155</v>
+        <v>0.6914163135075507</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.702180917538801</v>
+        <v>0.6862138782805398</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.7012450167910578</v>
+        <v>0.6794768590598403</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.6966458029337225</v>
+        <v>0.6900536545859486</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.6201318150400402</v>
+        <v>0.6829771488015862</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.6090547786442879</v>
+        <v>0.6952028541307398</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.6056347787839225</v>
+        <v>0.6691444240422814</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.6099397127716765</v>
+        <v>0.6537137561002855</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.5878558063547696</v>
+        <v>0.6507566448604003</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.5452859367036466</v>
+        <v>0.6530325139110946</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.5451806871417501</v>
+        <v>0.6426503340757239</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.5414234697795869</v>
+        <v>0.6454037533774113</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.5414234697795869</v>
+        <v>0.6447767941297624</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.5160270821260761</v>
+        <v>0.6291684411894073</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.5193723774881136</v>
+        <v>0.6664861307957076</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.5175639351816297</v>
+        <v>0.6458020610063464</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.5175639351816297</v>
+        <v>0.6432591408284519</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.5175639351816297</v>
+        <v>0.640858822461618</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.5169369759339808</v>
+        <v>0.6130575783175429</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.5156151601259504</v>
+        <v>0.5902391940292255</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.5253352975263734</v>
+        <v>0.5422631972128938</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.529859806885381</v>
+        <v>0.5435850130209242</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.5248418638423246</v>
+        <v>0.5317871131249521</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5235528621597281</v>
+        <v>0.5177461583037192</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.4992723293141848</v>
+        <v>0.5173975954925959</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5012912707444618</v>
+        <v>0.5094995147698473</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5047395466065308</v>
+        <v>0.5104422227031857</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5042178369207784</v>
+        <v>0.5101638262666601</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5072824667844251</v>
+        <v>0.5079740070236192</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5075959464082496</v>
+        <v>0.510201178515824</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5078041764701775</v>
+        <v>0.5115229943238545</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5014293344317921</v>
+        <v>0.5128448101318849</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5014293344317921</v>
+        <v>0.5146555215002339</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5014293344317921</v>
+        <v>0.5589851358993514</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5016726476810188</v>
+        <v>0.5575954227785884</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5009755220587722</v>
+        <v>0.5569684635309395</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5015673981191222</v>
+        <v>0.560521988954905</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5015673981191222</v>
+        <v>0.5489605951225642</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5024048564905642</v>
+        <v>0.5531433488560438</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5024048564905642</v>
+        <v>0.5687494327345337</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5092685940892684</v>
+        <v>0.5687494327345337</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5041827537334795</v>
+        <v>0.5577425627133791</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5041827537334795</v>
+        <v>0.5561491576544184</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5041476705461806</v>
+        <v>0.540648323337825</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5049477766684586</v>
+        <v>0.5775280840041611</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5046342970446341</v>
+        <v>0.5775280840041611</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5046342970446341</v>
+        <v>0.570302169223143</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5025780033651933</v>
+        <v>0.568110080918237</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5025780033651933</v>
+        <v>0.568110080918237</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5031698794255434</v>
+        <v>0.5999186628592972</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.4999343717491325</v>
+        <v>0.6058318380797453</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5028563998017189</v>
+        <v>0.6064237141400953</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5022645237413689</v>
+        <v>0.6037404612130056</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5025780033651933</v>
+        <v>0.5979587170375128</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5025780033651933</v>
+        <v>0.5825959464082496</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5025780033651933</v>
+        <v>0.5826310295955485</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5022645237413689</v>
+        <v>0.5800134049193262</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5022645237413689</v>
+        <v>0.5623704016588588</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5006971256222466</v>
+        <v>0.5141263064560047</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5011158548079676</v>
+        <v>0.5141263064560047</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5017428140556165</v>
+        <v>0.5139180763940767</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5017428140556165</v>
+        <v>0.4950651395298504</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5017428140556165</v>
+        <v>0.4202093122298944</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5017428140556165</v>
+        <v>0.5023882748846269</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5017428140556165</v>
+        <v>0.50882874517388</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5013591680571944</v>
+        <v>0.5360175171575986</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5013591680571944</v>
+        <v>0.5351098924115589</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.4994782903142476</v>
+        <v>0.5067382410232422</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5004187291857209</v>
+        <v>0.5027342195474443</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5006971256222466</v>
+        <v>0.5027342195474443</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.4995835398761441</v>
+        <v>0.5032887433586305</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.4995835398761441</v>
+        <v>0.5131628278794396</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.4981236603807835</v>
+        <v>0.4974050659424287</v>
       </c>
     </row>
   </sheetData>
